--- a/data/trans_bre/P8_2_R-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P8_2_R-Clase-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,77; 10,0</t>
+          <t>-0,78; 9,64</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-6,16; 4,02</t>
+          <t>-6,0; 4,33</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,77; 5,17</t>
+          <t>-4,99; 5,17</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,45</t>
+          <t>-0,03; 6,22</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-5,77; 104,09</t>
+          <t>-5,87; 105,07</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-39,23; 37,26</t>
+          <t>-38,55; 43,0</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-34,94; 56,98</t>
+          <t>-36,41; 56,37</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,24; 89,56</t>
+          <t>-0,42; 85,5</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-4,23; 4,05</t>
+          <t>-5,09; 3,66</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-4,78; 5,02</t>
+          <t>-4,95; 4,78</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-3,18; 6,09</t>
+          <t>-3,26; 6,63</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,41; 6,59</t>
+          <t>-1,28; 6,86</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-40,93; 68,07</t>
+          <t>-46,59; 53,87</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-36,23; 56,26</t>
+          <t>-37,68; 52,16</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-25,98; 75,78</t>
+          <t>-24,98; 83,44</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-10,39; 68,22</t>
+          <t>-9,41; 73,14</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,83; 18,64</t>
+          <t>4,19; 19,34</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,69; 15,63</t>
+          <t>2,05; 15,05</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,44; 18,84</t>
+          <t>3,98; 20,07</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-55,83; 11,65</t>
+          <t>-54,15; 12,17</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>27,61; 162,14</t>
+          <t>29,13; 171,27</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,34; 92,07</t>
+          <t>9,31; 91,16</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>20,18; 135,83</t>
+          <t>20,98; 142,56</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-70,69; 71,32</t>
+          <t>-71,31; 72,34</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,49; 4,85</t>
+          <t>-2,17; 5,36</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-6,56; 1,01</t>
+          <t>-6,61; 0,95</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-4,35; 2,53</t>
+          <t>-4,75; 2,14</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-13,7; -1,94</t>
+          <t>-14,29; -2,32</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-12,1; 27,53</t>
+          <t>-11,14; 30,98</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-31,89; 6,74</t>
+          <t>-32,39; 5,67</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-24,0; 17,58</t>
+          <t>-26,51; 14,33</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-66,05; -10,61</t>
+          <t>-64,78; -11,81</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 9,74</t>
+          <t>-0,96; 9,21</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>10,68; 20,72</t>
+          <t>10,82; 20,66</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,19; 12,38</t>
+          <t>3,47; 12,72</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,7; 11,04</t>
+          <t>-2,6; 11,53</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,23; 76,86</t>
+          <t>-5,77; 66,54</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>53,73; 143,13</t>
+          <t>54,36; 143,53</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,93; 68,98</t>
+          <t>14,66; 69,18</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-6,73; 58,09</t>
+          <t>-9,7; 60,9</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>25,63; 32,11</t>
+          <t>25,72; 32,11</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>26,75; 35,1</t>
+          <t>26,83; 34,84</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>25,34; 32,38</t>
+          <t>25,25; 32,19</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>26,96; 33,94</t>
+          <t>27,61; 34,19</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>470,14; 1762,54</t>
+          <t>448,94; 1644,77</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>374,27; 1793,78</t>
+          <t>385,72; 1709,87</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>558,5; 3666,87</t>
+          <t>584,4; 3749,64</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>593,48; 3340,3</t>
+          <t>594,83; 2942,11</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>7,57; 11,18</t>
+          <t>7,36; 11,1</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>8,05; 12,12</t>
+          <t>8,18; 12,18</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6,16; 10,06</t>
+          <t>6,22; 10,22</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-20,05; 6,77</t>
+          <t>-18,55; 7,17</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>51,58; 85,57</t>
+          <t>49,81; 84,25</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>48,25; 82,99</t>
+          <t>49,75; 82,38</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>39,43; 73,95</t>
+          <t>40,53; 75,23</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-48,06; 44,92</t>
+          <t>-48,22; 47,84</t>
         </is>
       </c>
     </row>
